--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260915.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260915.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>15.36%</t>
+          <t>15.71%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>6.64%</t>
+          <t>6.58%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.21%</t>
+          <t>5.97%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.63%</t>
+          <t>5.50%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.40%</t>
+          <t>5.41%</t>
         </is>
       </c>
     </row>
@@ -726,51 +726,51 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.16%</t>
+          <t>5.12%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>1,115,000</t>
+          <t>1,100,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.27%</t>
+          <t>4.02%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>1,100,000</t>
+          <t>1,115,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>3.98%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>3.09%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>3.09%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>2.89%</t>
         </is>
       </c>
     </row>
@@ -880,29 +880,29 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.51%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>536,000</t>
+          <t>2,770,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.02%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
@@ -941,100 +941,100 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>3,550,000</t>
+          <t>3,700,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>2,640,000</t>
+          <t>1,900,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.75%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>1,900,000</t>
+          <t>2,800,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>2,800,000</t>
+          <t>1,293,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>1,293,000</t>
+          <t>380,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
@@ -1144,178 +1144,178 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>130,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.54%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>130,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>2,600,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,600,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,100,000</t>
+          <t>800,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>350,000</t>
+          <t>1,100,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>800,000</t>
+          <t>350,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.13%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.06%</t>
         </is>
       </c>
     </row>
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>8,598,485,395</t>
+          <t>8,362,926,078</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>1,371,365,473</t>
+          <t>1,422,387,891</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
